--- a/cache/Bank_vaset.xlsx
+++ b/cache/Bank_vaset.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\milad\Desktop\milad_repo\cache\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EDA5B18-F4F4-4B3D-ABFC-93C6422FA7F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33B1D4EF-2896-4F3D-91CE-F46FF4E4BBF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{31097255-E4FF-4670-A9F1-99044B3A5D90}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{31097255-E4FF-4670-A9F1-99044B3A5D90}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="52">
   <si>
     <t>حساب بانكي كد تفصيل</t>
   </si>
@@ -44,75 +44,27 @@
     <t>001</t>
   </si>
   <si>
-    <t>002</t>
-  </si>
-  <si>
-    <t>003</t>
-  </si>
-  <si>
-    <t>004</t>
-  </si>
-  <si>
-    <t>005</t>
-  </si>
-  <si>
-    <t>006</t>
-  </si>
-  <si>
     <t>007</t>
   </si>
   <si>
     <t>008</t>
   </si>
   <si>
-    <t>009</t>
-  </si>
-  <si>
-    <t>010</t>
-  </si>
-  <si>
-    <t>011</t>
-  </si>
-  <si>
-    <t>012</t>
-  </si>
-  <si>
     <t>013</t>
   </si>
   <si>
-    <t>014</t>
-  </si>
-  <si>
-    <t>015</t>
-  </si>
-  <si>
     <t>حساب بانكي بانك و شعبه</t>
   </si>
   <si>
     <t>پارسيان فلكه فيض</t>
   </si>
   <si>
-    <t>ملي سه راه نظر</t>
-  </si>
-  <si>
-    <t>بانك شهر اصفهان</t>
-  </si>
-  <si>
     <t>ملي مارال</t>
   </si>
   <si>
     <t>ملي مارينا</t>
   </si>
   <si>
-    <t>ملي مجيد حلبيان</t>
-  </si>
-  <si>
-    <t>ملت اصفهان</t>
-  </si>
-  <si>
-    <t>ملت خانم غلامعليان</t>
-  </si>
-  <si>
     <t>بانك مهر اصفهان</t>
   </si>
   <si>
@@ -125,46 +77,121 @@
     <t>پارسيان فلكه فيض 200320101550968601</t>
   </si>
   <si>
-    <t>ملي سه راه نظر 0118164594002</t>
-  </si>
-  <si>
-    <t>بانك شهر اصفهان 4001000356004</t>
-  </si>
-  <si>
-    <t>بانك شهر اصفهان 1001001385240</t>
-  </si>
-  <si>
-    <t>ملي سه راه نظر 0234000024008</t>
-  </si>
-  <si>
-    <t>ملي سه راه نظر 0366524661002</t>
-  </si>
-  <si>
     <t>ملي مارال 0370299746007</t>
   </si>
   <si>
     <t>ملي مارينا 0235110283004</t>
   </si>
   <si>
-    <t>ملي مجيد حلبيان 0367290066007</t>
-  </si>
-  <si>
-    <t>ملت اصفهان 1357429476</t>
-  </si>
-  <si>
-    <t>ملت اصفهان 2063616092</t>
-  </si>
-  <si>
-    <t>ملت خانم غلامعليان 0747059517</t>
-  </si>
-  <si>
     <t>بانك مهر اصفهان ‎⁮2401-10-16152243-1‬</t>
   </si>
   <si>
-    <t>بانك مهر اصفهان ‎⁮2401-700-16152243-1‬</t>
-  </si>
-  <si>
-    <t>پارسيان فلكه فيض 200347001880368601</t>
+    <t>bank</t>
+  </si>
+  <si>
+    <t>coding</t>
+  </si>
+  <si>
+    <t>activation</t>
+  </si>
+  <si>
+    <t>activationidx</t>
+  </si>
+  <si>
+    <t>armpicture</t>
+  </si>
+  <si>
+    <t>defalt</t>
+  </si>
+  <si>
+    <t>protocol</t>
+  </si>
+  <si>
+    <t>protocol_idx</t>
+  </si>
+  <si>
+    <t>portnum</t>
+  </si>
+  <si>
+    <t>terminal_serial</t>
+  </si>
+  <si>
+    <t>terminal_id</t>
+  </si>
+  <si>
+    <t>code_pazirandeh</t>
+  </si>
+  <si>
+    <t>ip</t>
+  </si>
+  <si>
+    <t>شماره 1(99387213)</t>
+  </si>
+  <si>
+    <t>فعال</t>
+  </si>
+  <si>
+    <t>تجارت الکترونيک پارسيان</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                    </t>
+  </si>
+  <si>
+    <t>شماره2(99387216)</t>
+  </si>
+  <si>
+    <t>شماره3(99387215)</t>
+  </si>
+  <si>
+    <t>شماره4(99387217)</t>
+  </si>
+  <si>
+    <t>شماره5(99387214)</t>
+  </si>
+  <si>
+    <t>مهر(6546423)</t>
+  </si>
+  <si>
+    <t>شرکت سامان کيش</t>
+  </si>
+  <si>
+    <t>پارسيان 1</t>
+  </si>
+  <si>
+    <t>172.20.20.114</t>
+  </si>
+  <si>
+    <t>پارسيان 2</t>
+  </si>
+  <si>
+    <t>172.20.20.111</t>
+  </si>
+  <si>
+    <t>پارسيان 3</t>
+  </si>
+  <si>
+    <t>172.20.20.113</t>
+  </si>
+  <si>
+    <t>متفرقه</t>
+  </si>
+  <si>
+    <t>پارسيان پايين</t>
+  </si>
+  <si>
+    <t>172.20.20.112</t>
+  </si>
+  <si>
+    <t>ملي پايين</t>
+  </si>
+  <si>
+    <t>شرکت سداد-بانک ملي</t>
+  </si>
+  <si>
+    <t>172.20.20.125</t>
+  </si>
+  <si>
+    <t>مانده بدهي</t>
   </si>
 </sst>
 </file>
@@ -222,10 +249,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -560,264 +589,738 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACBF8904-44C2-442E-AAA7-1BD63394DE97}">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr defaultColWidth="14" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="35.5703125" customWidth="1"/>
-    <col min="4" max="4" width="25.7109375" customWidth="1"/>
+    <col min="1" max="2" width="18.5703125" customWidth="1"/>
+    <col min="3" max="3" width="30.28515625" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" customWidth="1"/>
+    <col min="5" max="5" width="31.5703125" customWidth="1"/>
+    <col min="6" max="6" width="35.5703125" customWidth="1"/>
+    <col min="7" max="7" width="25.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O1" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="P1" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="Q1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>15</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2">
+        <v>3008</v>
+      </c>
+      <c r="G2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <v>2020</v>
+      </c>
+      <c r="N2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O2">
+        <v>99387213</v>
+      </c>
+      <c r="P2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q2">
+        <v>111111</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="B3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3">
+        <v>3008</v>
+      </c>
+      <c r="G3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3">
+        <v>3</v>
+      </c>
+      <c r="M3">
+        <v>2020</v>
+      </c>
+      <c r="N3" t="s">
+        <v>32</v>
+      </c>
+      <c r="O3">
+        <v>99387216</v>
+      </c>
+      <c r="P3" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q3">
+        <v>111111</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="B4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4">
+        <v>3008</v>
+      </c>
+      <c r="G4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4" t="s">
+        <v>31</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
+      </c>
+      <c r="M4">
+        <v>2020</v>
+      </c>
+      <c r="N4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O4">
+        <v>99387215</v>
+      </c>
+      <c r="P4" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q4">
+        <v>1111111</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>18</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5">
+        <v>3008</v>
+      </c>
+      <c r="G5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5" t="s">
+        <v>31</v>
+      </c>
+      <c r="L5">
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <v>2020</v>
+      </c>
+      <c r="N5" t="s">
+        <v>32</v>
+      </c>
+      <c r="O5">
+        <v>99387217</v>
+      </c>
+      <c r="P5" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q5">
+        <v>111111</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>19</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6">
+        <v>3008</v>
+      </c>
+      <c r="G6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6" t="s">
+        <v>31</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>2020</v>
+      </c>
+      <c r="N6" t="s">
+        <v>32</v>
+      </c>
+      <c r="O6">
+        <v>99387214</v>
+      </c>
+      <c r="P6" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q6">
+        <v>1111111</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>20</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7">
+        <v>3015</v>
+      </c>
+      <c r="G7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7" t="s">
+        <v>38</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>2020</v>
+      </c>
+      <c r="N7" t="s">
+        <v>32</v>
+      </c>
+      <c r="O7">
+        <v>6546423</v>
+      </c>
+      <c r="P7" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q7">
+        <v>11111</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>8</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8">
+        <v>3008</v>
+      </c>
+      <c r="G8" t="s">
+        <v>30</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L8">
+        <v>3</v>
+      </c>
+      <c r="M8">
+        <v>2020</v>
+      </c>
+      <c r="N8">
+        <v>53453453453</v>
+      </c>
+      <c r="O8">
+        <v>435453</v>
+      </c>
+      <c r="P8">
+        <v>43453453</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>9</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9">
+        <v>3008</v>
+      </c>
+      <c r="G9" t="s">
+        <v>30</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L9">
+        <v>3</v>
+      </c>
+      <c r="M9">
+        <v>2020</v>
+      </c>
+      <c r="N9" t="s">
+        <v>32</v>
+      </c>
+      <c r="O9" t="s">
+        <v>32</v>
+      </c>
+      <c r="P9" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>10</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10">
+        <v>3008</v>
+      </c>
+      <c r="G10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10" t="s">
+        <v>31</v>
+      </c>
+      <c r="L10">
+        <v>3</v>
+      </c>
+      <c r="M10">
+        <v>2020</v>
+      </c>
+      <c r="N10" t="s">
+        <v>32</v>
+      </c>
+      <c r="O10" t="s">
+        <v>32</v>
+      </c>
+      <c r="P10" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>12</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11">
+        <v>3010</v>
+      </c>
+      <c r="G11" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11" t="s">
+        <v>31</v>
+      </c>
+      <c r="L11">
+        <v>3</v>
+      </c>
+      <c r="M11">
+        <v>2020</v>
+      </c>
+      <c r="N11">
+        <v>52372357</v>
+      </c>
+      <c r="O11">
+        <v>7522785782</v>
+      </c>
+      <c r="P11">
+        <v>7527728</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>31</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4">
+      <c r="C12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>32</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="C13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>45</v>
+      </c>
+      <c r="F14">
+        <v>3009</v>
+      </c>
+      <c r="G14" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>31</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>32</v>
-      </c>
-      <c r="B9" s="1" t="s">
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>32</v>
+      </c>
+      <c r="O14" t="s">
+        <v>32</v>
+      </c>
+      <c r="P14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="E15" t="s">
+        <v>48</v>
+      </c>
+      <c r="F15">
+        <v>3011</v>
+      </c>
+      <c r="G15" t="s">
+        <v>30</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15">
         <v>8</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15">
+      <c r="M15">
+        <v>8009</v>
+      </c>
+      <c r="N15">
+        <v>52372357</v>
+      </c>
+      <c r="O15">
+        <v>7522785782</v>
+      </c>
+      <c r="P15">
+        <v>7527728</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16">
         <v>14</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>7</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>8</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="E16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F16">
+        <v>3014</v>
+      </c>
+      <c r="G16" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>32</v>
+      </c>
+      <c r="O16" t="s">
+        <v>32</v>
+      </c>
+      <c r="P16" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D17" s="3"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+    </row>
+    <row r="18" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D18" s="3"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+    </row>
+    <row r="19" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+    </row>
+    <row r="21" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/cache/Bank_vaset.xlsx
+++ b/cache/Bank_vaset.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\milad\Desktop\milad_repo\cache\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33B1D4EF-2896-4F3D-91CE-F46FF4E4BBF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F02F809-EBBE-4C8D-B295-598A68235347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{31097255-E4FF-4670-A9F1-99044B3A5D90}"/>
+    <workbookView xWindow="915" yWindow="1860" windowWidth="21600" windowHeight="11385" xr2:uid="{31097255-E4FF-4670-A9F1-99044B3A5D90}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="59">
   <si>
     <t>حساب بانكي كد تفصيل</t>
   </si>
@@ -192,6 +192,27 @@
   </si>
   <si>
     <t>مانده بدهي</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>ملي سه راه نظر 0118164594002</t>
+  </si>
+  <si>
+    <t>ملي سه راه نظر</t>
+  </si>
+  <si>
+    <t>005</t>
+  </si>
+  <si>
+    <t>ملي سه راه نظر 0234000024008</t>
+  </si>
+  <si>
+    <t>006</t>
+  </si>
+  <si>
+    <t>ملي سه راه نظر 0366524661002</t>
   </si>
 </sst>
 </file>
@@ -249,12 +270,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1181,39 +1200,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>11</v>
-      </c>
-      <c r="E14" t="s">
-        <v>45</v>
-      </c>
-      <c r="F14">
-        <v>3009</v>
-      </c>
-      <c r="G14" t="s">
-        <v>30</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>1</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14" t="s">
-        <v>32</v>
-      </c>
-      <c r="O14" t="s">
-        <v>32</v>
-      </c>
-      <c r="P14" t="s">
-        <v>32</v>
+        <v>1</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -1292,35 +1290,87 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D17" s="3"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-    </row>
-    <row r="18" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D18" s="3"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-    </row>
-    <row r="19" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-    </row>
-    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-    </row>
-    <row r="21" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>2</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>5</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>6</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>45</v>
+      </c>
+      <c r="F21">
+        <v>3009</v>
+      </c>
+      <c r="G21" t="s">
+        <v>30</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>32</v>
+      </c>
+      <c r="O21" t="s">
+        <v>32</v>
+      </c>
+      <c r="P21" t="s">
+        <v>32</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
